--- a/site/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Conditional Writeback Settings</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,129 +649,129 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KS7EYPT5R5R60900YZ4SDYP9</t>
+          <t>h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7EYPT5R5R60900YZ4SDYP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Setting</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
+          <t>h_01KS06157W1F8XZJ82X34B3PQH</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7EYQNAVT985NR9FA2P8WSJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157W1F8XZJ82X34B3PQH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KS06157W1F8XZJ82X34B3PQH</t>
+          <t>h_01KS06157WYJGAJCAK99BH8GJG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157W1F8XZJ82X34B3PQH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157WYJGAJCAK99BH8GJG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KS06157WYJGAJCAK99BH8GJG</t>
+          <t>h_01KS06157W2NNBJH667KQXM109</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157WYJGAJCAK99BH8GJG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157W2NNBJH667KQXM109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADP Application Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KS06157W2NNBJH667KQXM109</t>
+          <t>h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS06157W2NNBJH667KQXM109</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
+          <t>h_01KS7K1N0D3FJKM470R3E359Q8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7JYH0ZFSHD8E247N3M4J8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7K1N0D3FJKM470R3E359Q8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,252 +781,186 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KS7K1N0D3FJKM470R3E359Q8</t>
+          <t>h_01KS7K248GDK85V96XFQVT95PG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7K1N0D3FJKM470R3E359Q8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7K248GDK85V96XFQVT95PG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KS7K248GDK85V96XFQVT95PG</t>
+          <t>h_01KSF555CC71J74RFD8PMJ59Q5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KS7K248GDK85V96XFQVT95PG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF555CC71J74RFD8PMJ59Q5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSF555CB87B97HG8T4V7KE3P</t>
+          <t>h_01KSF692ZET6DJF36H38243661</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF555CB87B97HG8T4V7KE3P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF692ZET6DJF36H38243661</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KSF555CBK35GX7APQKF9XT7V</t>
+          <t>h_01KSF6AB4WC1EGWF4T9DQQ9Y8X</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF555CBK35GX7APQKF9XT7V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6AB4WC1EGWF4T9DQQ9Y8X</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Insights Settings</t>
+          <t>Configurations</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KSF555CC71J74RFD8PMJ59Q5</t>
+          <t>h_01KSF6NMARH2GC42AB0TH8JH60</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF555CC71J74RFD8PMJ59Q5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6NMARH2GC42AB0TH8JH60</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Adding a Notification Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KSF692ZET6DJF36H38243661</t>
+          <t>h_01KSF6WGM8EKYE6ZAR5BP91GJR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF692ZET6DJF36H38243661</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6WGM8EKYE6ZAR5BP91GJR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KSF6AB4WC1EGWF4T9DQQ9Y8X</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6AB4WC1EGWF4T9DQQ9Y8X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Configurations</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSF6NMARH2GC42AB0TH8JH60</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6NMARH2GC42AB0TH8JH60</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adding a Notification Configuration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KSF6WGM8EKYE6ZAR5BP91GJR</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01KSF6WGM8EKYE6ZAR5BP91GJR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Entra-ID-Writeback-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
